--- a/Documents/Product Catalog/4 Product.xlsx
+++ b/Documents/Product Catalog/4 Product.xlsx
@@ -1545,7 +1545,7 @@
         <v/>
       </c>
       <c r="L8" s="14" t="n">
-        <v>17100</v>
+        <v>17990</v>
       </c>
       <c r="M8" s="15" t="n">
         <v>0.1</v>
